--- a/out/SBOX_REV9_BOM.xlsx
+++ b/out/SBOX_REV9_BOM.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="231">
   <si>
     <r>
       <rPr>
@@ -2003,6 +2003,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">규격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">길이 </t>
     </r>
     <r>
@@ -2020,6 +2037,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">레일 확인 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(HOLD 2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SCOUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">레일 </t>
     </r>
     <r>
@@ -2037,17 +2082,1192 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">너트 확인 후 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(HOLD 2)</t>
-    </r>
+      <t xml:space="preserve">너트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">레일 규격 따름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOLD 2 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레일 피치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">홈 폭 확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M3×10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">육각홈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ M3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나일록 너트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와셔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D-size </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커넥터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">육각 스탠드오프 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M-F 25 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Al </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 황동</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AGX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트레이</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30/35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B0473 fit check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(HOLD 5)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">육각 스탠드오프 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M-F 30 / 35</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AGX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트레이 높이 조정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">옵션</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">블라인드 리벳 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ø3.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">돔헤드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그립 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.0~4.8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Al/Al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벽 스플라이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제작사 조립 시 제작사 지급 가능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">육각 스탠드오프 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M-F 10 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전장판</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M4×8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버튼헤드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ISO 7380)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P10 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스탠드오프</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">볼트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나일론 스페이서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나일록 너트 키트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon/SUS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부품 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DC/DC, CAN Pal, WAGO, 5G)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 6~20mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M3×8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">육각홈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(OS1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SUS / 12.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS1 → P05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">길이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: OS1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나사 깊이 확인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(HOLD 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M2×6 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">너트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스페이서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 모듈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0473 ×6 → P06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLD 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTOR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 글랜드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M16×1.5 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로크너트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클램프 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.5~10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">니켈황동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IP68 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Lapp SKINTOP MS-M 16)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P07 — SCOUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확장 케이블</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">케이블 외경 확인</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분할형 케이블 글랜드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M32 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커넥터 통과형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IP54 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P04 — OS1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OS1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 외경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커넥터 확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">etherCON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피드스루 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D-size (Neutrik NE8FDP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 동등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cat6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07 D1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USB 3.0 A↔A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피드스루 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D-size (Neutrik NAUSB3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 동등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P07 D2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D-size </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">블랭크 플레이트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 12V DC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D-size</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P07 D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SMA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벌크헤드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(F) – U.FL/IPEX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피그테일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15cm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">50Ω</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07 SMA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모뎀 확정 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(HOLD 7)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRICAL</t>
   </si>
   <si>
     <r>
@@ -2065,94 +3285,814 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">레일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">너트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">레일 규격 따름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레일</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOLD 2 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레일 슬롯 폭 확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M3×10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육각홈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ M3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나일록 너트 </t>
+      <t xml:space="preserve">확장 케이블</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동봉 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핀 항공 플러그 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 4C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(AWG18 ×2 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트위스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CAN) 1 m</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">납땜 제작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위고 제작 요청 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불가 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KETI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">납땜</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arducam 15-22pin FPC 60cm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Arducam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정품</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">먼 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 카메라</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30cm ×6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 60cm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">별도</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인라인 퓨즈홀더 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWG16~18 + ATO 5A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퓨즈</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인입</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퓨즈 예비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WAGO 221-413 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레버 커넥터</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3P</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24V/GND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분배</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전선 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWG18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">흑</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">UL1015</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">m</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트위스트 페어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWG24</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN (m)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배럴 플러그 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.5/2.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피그테일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AGX J41</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DC/DC 24→12V (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존품 사양 미달 시에만 대체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19~36V, 12V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속 ≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8A (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Mean Well SD-100B-12)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장착</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOLD 6 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존품 실측 후 수량 결정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">듀폰 점퍼 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F-F 20cm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN Pal ↔ J30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPDM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폼 테이프 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10×3 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하판 가스켓 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(m)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">옵션 방진</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPDM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">패드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1t 110×110</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벨크로 스트랩 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25mm × 300</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AGX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 타이 </t>
     </r>
     <r>
       <rPr>
@@ -2169,509 +4109,46 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">와셔</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D-size </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커넥터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육각 스탠드오프 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M-F 25 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Al </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 황동</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AGX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트레이</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30/35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B0473 fit check </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결과 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(HOLD 5)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육각 스탠드오프 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M-F 30 / 35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AGX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트레이 높이 조정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">옵션</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">블라인드 리벳 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ø3.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">돔헤드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그립 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.0~4.8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Al/Al</t>
-  </si>
-  <si>
-    <t xml:space="preserve">벽 스플라이스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제작사 조립 시 제작사 지급 가능</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육각 스탠드오프 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M-F 10 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전장판</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M4×8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">버튼헤드 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ISO 7380)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P10 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스탠드오프</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">볼트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나일론 스페이서 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나일록 너트 키트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Nylon/SUS</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부품 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DC/DC, CAN Pal, WAGO, 5G)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 6~20mm</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M3×8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육각홈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(OS1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장착</t>
+      <t xml:space="preserve">타이 마운트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(M3)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">하네스</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나사 고착제 중강도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Loctite 243 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등</t>
     </r>
     <r>
       <rPr>
@@ -2684,56 +4161,215 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">SUS / 12.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OS1 → P05</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">길이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: OS1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나사 깊이 확인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(HOLD 3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M2×6 + </t>
+    <t xml:space="preserve">OPTION</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OPT-2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벤트 방진 메쉬 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SUS 100mesh, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내측 접착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1/C3/C4/C6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벤트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">분진 환경 시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOLD </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">해제 방법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판금 발주 영향</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완료일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SCOUT 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핀 항공 플러그 모델</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동봉 플러그에 케이블 납땜 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">글랜드 통과</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/KETI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레일 피치 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">230 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">홈 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ T-</t>
     </r>
     <r>
       <rPr>
@@ -2743,992 +4379,32 @@
       </rPr>
       <t xml:space="preserve">너트</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스페이서 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카메라 모듈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0473 ×6 → P06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLD 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONNECTOR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">케이블 글랜드 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M16×1.5 + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로크너트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클램프 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.5~10)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">니켈황동 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IP68 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: Lapp SKINTOP MS-M 16)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P07 — SCOUT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피그테일</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">피그테일 외경 확인</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분할형 케이블 글랜드 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M32 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커넥터 통과형</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IP54 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P04 — OS1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">케이블</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OS1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">케이블 외경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커넥터 확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">etherCON </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피드스루 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D-size (Neutrik NE8FDP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 동등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Cat6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P07 D1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">USB 3.0 A↔A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피드스루 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D-size (Neutrik NAUSB3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 동등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P07 D2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D-size </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">블랭크 플레이트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ 12V DC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">잭 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D-size</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P07 D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">선택</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SMA </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">벌크헤드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(F) – U.FL/IPEX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피그테일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15cm</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">50Ω</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P07 SMA</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5G </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모뎀 확정 후 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(HOLD 7)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ELECTRICAL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ATO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인라인 퓨즈홀더 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AWG16~18 + ATO 5A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">퓨즈</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24V </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인입</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">퓨즈 예비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WAGO 221-413 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레버 커넥터</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">3P</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24V/GND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분배</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전선 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AWG18 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">흑</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">UL1015</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(m)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">m</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트위스트 페어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AWG24</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN (m)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배럴 플러그 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.5/2.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피그테일</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">센터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">AGX J41</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC/DC 24→12V (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기존품 사양 미달 시에만 대체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19~36V, 12V </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연속 ≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8A (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: Mean Well SD-100B-12)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장착</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOLD 6 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기존품 실측 후 수량 결정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">듀폰 점퍼 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F-F 20cm</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN Pal ↔ J30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPDM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">폼 테이프 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10×3 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커버</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매뉴얼 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도면</t>
     </r>
     <r>
       <rPr>
@@ -3745,462 +4421,47 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">하판 가스켓 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(m)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">옵션 방진</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPDM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">패드 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1t 110×110</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">벨크로 스트랩 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25mm × 300</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AGX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">케이블 타이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타이 마운트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(M3)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">하네스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나사 고착제 중강도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Loctite 243 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">OPTION</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OPT-2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">벤트 방진 메쉬 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(SUS 100mesh, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내측 접착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C1/C3/C4/C6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">벤트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">분진 환경 시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOLD </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">항목</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">해제 방법</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판금 발주 영향</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">완료일</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SCOUT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메이팅 커넥터 셸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">성별</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급 피그테일 사용 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">글랜드 통과</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">없음 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본체 발주 가능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위고 회신으로 확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">슬롯 가공 전 필수</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">KETI</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">너트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">볼트 규격</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실물 레일 확인 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">길이 확정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">없음</t>
   </si>
   <si>
     <r>
@@ -6989,7 +7250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7718,29 +7979,31 @@
       </c>
       <c r="K24" s="13"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>148</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="7" t="s">
+        <v>150</v>
+      </c>
       <c r="D25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
         <f aca="false">D25+E25</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="12" t="n">
@@ -7751,28 +8014,30 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
         <f aca="false">D26+E26</f>
-        <v>6</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>157</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="12" t="n">
         <f aca="false">F26*I26</f>
@@ -7784,27 +8049,25 @@
       <c r="A27" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="B27" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="4"/>
       <c r="D27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="n">
         <f aca="false">D27+E27</f>
         <v>3</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>157</v>
+      <c r="G27" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="12" t="n">
@@ -7817,26 +8080,26 @@
       <c r="A28" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>162</v>
+      </c>
       <c r="D28" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="n">
         <f aca="false">D28+E28</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>158</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="H28" s="4"/>
       <c r="I28" s="5"/>
       <c r="J28" s="12" t="n">
         <f aca="false">F28*I28</f>
@@ -7848,26 +8111,28 @@
       <c r="A29" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>162</v>
+      <c r="B29" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
         <f aca="false">D29+E29</f>
-        <v>2</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="I29" s="5"/>
       <c r="J29" s="12" t="n">
         <f aca="false">F29*I29</f>
@@ -7875,30 +8140,28 @@
       </c>
       <c r="K29" s="13"/>
     </row>
-    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>165</v>
-      </c>
+      <c r="B30" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
         <f aca="false">D30+E30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>167</v>
       </c>
       <c r="I30" s="5"/>
@@ -7912,22 +8175,24 @@
       <c r="A31" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="D31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4" t="n">
         <f aca="false">D31+E31</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="5"/>
@@ -7937,29 +8202,31 @@
       </c>
       <c r="K31" s="13"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C32" s="4"/>
+        <v>173</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>174</v>
+      </c>
       <c r="D32" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
         <f aca="false">D32+E32</f>
-        <v>2</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>173</v>
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="12" t="n">
@@ -7970,24 +8237,24 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>174</v>
+        <v>148</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" s="4" t="n">
         <f aca="false">D33+E33</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="5"/>
@@ -7999,26 +8266,28 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
         <f aca="false">D34+E34</f>
-        <v>3</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H34" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>182</v>
+      </c>
       <c r="I34" s="5"/>
       <c r="J34" s="12" t="n">
         <f aca="false">F34*I34</f>
@@ -8028,24 +8297,24 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
         <f aca="false">D35+E35</f>
-        <v>20</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>178</v>
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="5"/>
@@ -8057,23 +8326,25 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
         <f aca="false">D36+E36</f>
-        <v>1</v>
-      </c>
-      <c r="G36" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="H36" s="4"/>
       <c r="I36" s="5"/>
       <c r="J36" s="12" t="n">
@@ -8084,28 +8355,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
         <f aca="false">D37+E37</f>
-        <v>4</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>183</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H37" s="4"/>
       <c r="I37" s="5"/>
       <c r="J37" s="12" t="n">
         <f aca="false">F37*I37</f>
@@ -8114,11 +8383,69 @@
       <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
+      <c r="A38" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <f aca="false">D38+E38</f>
+        <v>1</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="12" t="n">
+        <f aca="false">F38*I38</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <f aca="false">D39+E39</f>
+        <v>4</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="12" t="n">
+        <f aca="false">F39*I39</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J38" s="10" t="n">
-        <f aca="false">SUM(J4:J37)</f>
+      <c r="J40" s="10" t="n">
+        <f aca="false">SUM(J4:J39)</f>
         <v>0</v>
       </c>
     </row>
@@ -8151,22 +8478,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8174,16 +8501,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -8192,16 +8519,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>196</v>
+        <v>204</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -8210,16 +8537,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -8228,16 +8555,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -8246,16 +8573,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -8264,16 +8591,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -8282,16 +8609,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -8319,7 +8646,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8327,47 +8654,47 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/out/SBOX_REV9_BOM.xlsx
+++ b/out/SBOX_REV9_BOM.xlsx
@@ -3294,32 +3294,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동봉 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">핀 항공 플러그 </t>
+      <t xml:space="preserve">: 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핀 항공 메이팅 플러그 </t>
     </r>
     <r>
       <rPr>
@@ -3366,7 +3349,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">납땜 제작</t>
+    <t xml:space="preserve">플러그 규격 위고 확인</t>
   </si>
   <si>
     <t xml:space="preserve">H1</t>
@@ -3378,24 +3361,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">위고 제작 요청 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불가 시 </t>
+      <t xml:space="preserve">확보 방법 위고 문의 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구매 또는 </t>
     </r>
     <r>
       <rPr>
@@ -3414,6 +3397,15 @@
       </rPr>
       <t xml:space="preserve">납땜</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">CABLE</t>
@@ -4284,17 +4276,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">핀 항공 플러그 모델</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동봉 플러그에 케이블 납땜 → </t>
+      <t xml:space="preserve">핀 항공 메이팅 플러그 규격</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위고 문의 → 플러그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">케이블 확보 후 </t>
     </r>
     <r>
       <rPr>
